--- a/results/log_pv_cap_fit/log_pv_cap_fit_capacities_effects.xlsx
+++ b/results/log_pv_cap_fit/log_pv_cap_fit_capacities_effects.xlsx
@@ -511,298 +511,298 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>log_gdp_cap</t>
+          <t>Households per capita</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-4.067</t>
+          <t>-7.489</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>-0.017</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-4.001</t>
+          <t>-7.472</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.767</t>
+          <t>-2.078</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>-0.071</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-2.007</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-0.707</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-0.063</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-0.704</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-0.095</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.083</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.012</t>
+          <t>-0.644</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-1.725</t>
+          <t>-0.409</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.075</t>
+          <t>-0.018</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-1.650</t>
+          <t>-0.391</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-0.216</t>
+          <t>-0.293</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.042</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-0.174</t>
+          <t>-0.236</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.121</t>
+          <t>-0.244</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.036</t>
+          <t>-0.073</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.085</t>
+          <t>-0.172</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>log_fcapacity</t>
+          <t>GDP per capita</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.824</t>
+          <t>-4.067</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.027</t>
+          <t>-0.066</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.797</t>
+          <t>-4.001</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-9.244</t>
+          <t>-0.767</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>-0.063</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-10.911</t>
+          <t>-0.704</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-10.538</t>
+          <t>-0.095</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>-0.083</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-11.844</t>
+          <t>-0.012</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>41.197</t>
+          <t>-1.725</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.791</t>
+          <t>-0.075</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>39.406</t>
+          <t>-1.650</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>10.340</t>
+          <t>-0.216</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2.007</t>
+          <t>-0.042</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>8.333</t>
+          <t>-0.174</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>6.638</t>
+          <t>-0.121</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1.977</t>
+          <t>-0.036</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>4.661</t>
+          <t>-0.085</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>log_hcapacity</t>
+          <t>Firms per capita</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-7.489</t>
+          <t>11.824</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.017</t>
+          <t>2.027</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-7.472</t>
+          <t>9.797</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.078</t>
+          <t>-9.244</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.071</t>
+          <t>1.667</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.007</t>
+          <t>-10.911</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.707</t>
+          <t>-10.538</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.644</t>
+          <t>-11.844</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.409</t>
+          <t>41.197</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.018</t>
+          <t>1.791</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.391</t>
+          <t>39.406</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.293</t>
+          <t>10.340</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.057</t>
+          <t>2.007</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.236</t>
+          <t>8.333</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-0.244</t>
+          <t>6.638</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.073</t>
+          <t>1.977</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.172</t>
+          <t>4.661</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>log_acapacity</t>
+          <t>Firm assets per capita</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>log_income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>log_hholds</t>
+          <t>Households</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>log_sunny_hours</t>
+          <t>Sunny hours</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
